--- a/TestData/LV_T2279_TMTI0036293_ApproveEventExpenseFormAsSecondLevelApproverSet1.xlsx
+++ b/TestData/LV_T2279_TMTI0036293_ApproveEventExpenseFormAsSecondLevelApproverSet1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{289FA6B7-0365-4C68-B115-376903CC51FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA22978A-F220-4EA2-8B3F-9F6B131BC47F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,6 +21,7 @@
     <sheet name="Approver" sheetId="4" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -537,17 +538,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>55</v>
       </c>
@@ -555,7 +556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>36</v>
       </c>
@@ -563,7 +564,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -571,7 +572,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>36</v>
       </c>
@@ -579,7 +580,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>55</v>
       </c>
@@ -595,14 +596,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{780E0E82-BFFE-42FB-A31B-AC0D9C5DE596}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>52</v>
       </c>
@@ -615,14 +616,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D588DDF-4567-4D40-8446-D6AC9693F696}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>54</v>
       </c>
@@ -635,25 +636,25 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -704,7 +705,7 @@
       </c>
       <c r="Q1" s="1"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -760,7 +761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>27</v>
       </c>
@@ -816,7 +817,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -872,7 +873,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -928,7 +929,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -993,13 +994,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>31</v>
       </c>
@@ -1007,7 +1008,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>34</v>
       </c>
@@ -1018,7 +1019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>35</v>
       </c>
@@ -1029,7 +1030,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>35</v>
       </c>
@@ -1040,7 +1041,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>35</v>
       </c>
@@ -1051,7 +1052,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>34</v>
       </c>
@@ -1081,13 +1082,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>31</v>
       </c>
@@ -1095,7 +1096,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -1106,7 +1107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -1117,7 +1118,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>47</v>
       </c>
@@ -1128,7 +1129,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>47</v>
       </c>
@@ -1139,7 +1140,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>47</v>
       </c>

--- a/TestData/LV_T2279_TMTI0036293_ApproveEventExpenseFormAsSecondLevelApproverSet1.xlsx
+++ b/TestData/LV_T2279_TMTI0036293_ApproveEventExpenseFormAsSecondLevelApproverSet1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA22978A-F220-4EA2-8B3F-9F6B131BC47F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE3387AE-90F4-421C-B5D4-9AF9BDB3C1A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,6 @@
     <sheet name="Approver" sheetId="4" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="55">
   <si>
     <t>LOB</t>
   </si>
@@ -100,9 +99,6 @@
   </si>
   <si>
     <t>Users</t>
-  </si>
-  <si>
-    <t>Sonika Goyal</t>
   </si>
   <si>
     <t>1-10</t>
@@ -550,7 +546,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -558,7 +554,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -566,7 +562,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -574,7 +570,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -582,7 +578,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -600,12 +596,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -620,12 +616,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -707,37 +703,37 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G2" t="s">
         <v>20</v>
       </c>
       <c r="H2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>17</v>
@@ -746,16 +742,16 @@
         <v>18</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>19</v>
       </c>
       <c r="Q2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R2">
         <v>1</v>
@@ -763,37 +759,37 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" t="s">
         <v>29</v>
       </c>
-      <c r="C3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="I3" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="H3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>17</v>
@@ -802,10 +798,10 @@
         <v>18</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>19</v>
@@ -819,49 +815,49 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4" t="s">
         <v>29</v>
       </c>
-      <c r="C4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="I4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H4" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="J4" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>19</v>
@@ -875,49 +871,49 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5" t="s">
         <v>29</v>
       </c>
-      <c r="C5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F5" t="s">
-        <v>37</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="I5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H5" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="J5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L5" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>19</v>
@@ -931,55 +927,55 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G6" t="s">
         <v>20</v>
       </c>
       <c r="H6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>19</v>
       </c>
       <c r="Q6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R6">
         <v>5</v>
@@ -1002,18 +998,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1021,10 +1017,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1032,10 +1028,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1043,10 +1039,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1054,10 +1050,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1090,18 +1086,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1109,10 +1105,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1120,10 +1116,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1131,10 +1127,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1142,10 +1138,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C6">
         <v>5</v>

--- a/TestData/LV_T2279_TMTI0036293_ApproveEventExpenseFormAsSecondLevelApproverSet1.xlsx
+++ b/TestData/LV_T2279_TMTI0036293_ApproveEventExpenseFormAsSecondLevelApproverSet1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE3387AE-90F4-421C-B5D4-9AF9BDB3C1A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{217E9A8D-DBBD-4A82-90EE-4CE6799CFDBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -179,9 +179,6 @@
     <t>8000.0</t>
   </si>
   <si>
-    <t>Bingo@12345</t>
-  </si>
-  <si>
     <t>App Name</t>
   </si>
   <si>
@@ -195,6 +192,9 @@
   </si>
   <si>
     <t>Dimitri Drone</t>
+  </si>
+  <si>
+    <t>Bingo@123456</t>
   </si>
 </sst>
 </file>
@@ -534,25 +534,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>35</v>
       </c>
@@ -560,7 +560,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>35</v>
       </c>
@@ -568,7 +568,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>35</v>
       </c>
@@ -576,9 +576,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -592,16 +592,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{780E0E82-BFFE-42FB-A31B-AC0D9C5DE596}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>50</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -612,16 +612,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D588DDF-4567-4D40-8446-D6AC9693F696}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -632,25 +632,25 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -701,7 +701,7 @@
       </c>
       <c r="Q1" s="1"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -709,7 +709,7 @@
         <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D2" t="s">
         <v>24</v>
@@ -757,7 +757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -813,7 +813,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -869,7 +869,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -925,7 +925,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -933,7 +933,7 @@
         <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D6" t="s">
         <v>24</v>
@@ -990,13 +990,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
@@ -1004,56 +1004,56 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>33</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>34</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>34</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>34</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>33</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1065,10 +1065,10 @@
     <hyperlink ref="A4" r:id="rId2" xr:uid="{6ED0707E-1A3D-41DE-9D1F-0C185E1F4903}"/>
     <hyperlink ref="A5" r:id="rId3" xr:uid="{A88A08DE-BC8D-44F4-B4A3-F3F45BEED893}"/>
     <hyperlink ref="B2" r:id="rId4" xr:uid="{88D13356-CD0F-4958-BE46-AB501B49D616}"/>
-    <hyperlink ref="B3" r:id="rId5" xr:uid="{A3E22827-39FB-4FC6-9EAC-DE7315BA0C81}"/>
-    <hyperlink ref="B4" r:id="rId6" xr:uid="{40CE1B5F-D441-448A-B738-F06B6852272B}"/>
-    <hyperlink ref="B5" r:id="rId7" xr:uid="{9113FABB-0C3A-4289-8CE2-6D7F89AA21FC}"/>
-    <hyperlink ref="B6" r:id="rId8" xr:uid="{DF18B413-84D1-46B9-BEF6-EAE88CF2CB16}"/>
+    <hyperlink ref="B3" r:id="rId5" xr:uid="{E3837D86-3E1E-4CC5-8FE8-46EB00805B8F}"/>
+    <hyperlink ref="B4" r:id="rId6" xr:uid="{1028D539-72BC-4E4B-85CB-39FD56F90D1D}"/>
+    <hyperlink ref="B5" r:id="rId7" xr:uid="{936351B8-10CD-44D6-93BB-83092E54A30E}"/>
+    <hyperlink ref="B6" r:id="rId8" xr:uid="{FDD52833-A2D2-416A-B9B9-1D1ED7B62440}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId9"/>
@@ -1078,13 +1078,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
@@ -1092,56 +1092,56 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>32</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>32</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>46</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>46</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>46</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1153,10 +1153,10 @@
     <hyperlink ref="A5" r:id="rId2" xr:uid="{49CDF971-88A0-478A-9ABD-0C13B137739B}"/>
     <hyperlink ref="A6" r:id="rId3" xr:uid="{DD33285A-BEC3-43E6-9CF7-C07B547F86A0}"/>
     <hyperlink ref="B2" r:id="rId4" xr:uid="{E884574A-2EFB-4087-B99B-32D65C06622B}"/>
-    <hyperlink ref="B3" r:id="rId5" xr:uid="{6105F52E-E972-4C98-B334-0EDCFCF9DD32}"/>
-    <hyperlink ref="B4" r:id="rId6" xr:uid="{DD20A5EF-1467-4F63-9B7E-9F173DA3A144}"/>
-    <hyperlink ref="B5" r:id="rId7" xr:uid="{37C79583-FD74-4201-9420-A533782C49EB}"/>
-    <hyperlink ref="B6" r:id="rId8" xr:uid="{889EEB08-DA51-4093-ADBB-2B4F74F1E660}"/>
+    <hyperlink ref="B3" r:id="rId5" xr:uid="{22973577-FF8F-47B9-A1BA-31535138D047}"/>
+    <hyperlink ref="B4" r:id="rId6" xr:uid="{0328F278-F446-47D2-B683-A183B06CEC59}"/>
+    <hyperlink ref="B5" r:id="rId7" xr:uid="{C801AEF9-1D53-42EB-83AD-883CA7EAC29F}"/>
+    <hyperlink ref="B6" r:id="rId8" xr:uid="{EF36177A-64C7-45BD-A85C-E274887E5403}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId9"/>

--- a/TestData/LV_T2279_TMTI0036293_ApproveEventExpenseFormAsSecondLevelApproverSet1.xlsx
+++ b/TestData/LV_T2279_TMTI0036293_ApproveEventExpenseFormAsSecondLevelApproverSet1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA5AF54E-4283-40AF-A50A-49BCE38BF577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D89474-4C8A-4D5B-9E1A-17D7858EB171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -191,10 +191,10 @@
     <t>Dimitri Drone</t>
   </si>
   <si>
-    <t>Bingo@1234567</t>
-  </si>
-  <si>
     <t>FVATestOpportunity Admin</t>
+  </si>
+  <si>
+    <t>Bingo@123456</t>
   </si>
 </sst>
 </file>
@@ -742,7 +742,7 @@
         <v>18</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>38</v>
@@ -798,7 +798,7 @@
         <v>18</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>38</v>
@@ -854,7 +854,7 @@
         <v>18</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>38</v>
@@ -910,7 +910,7 @@
         <v>18</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>38</v>
@@ -966,7 +966,7 @@
         <v>18</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>38</v>
@@ -1009,7 +1009,7 @@
         <v>32</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1020,7 +1020,7 @@
         <v>33</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1031,7 +1031,7 @@
         <v>33</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1042,7 +1042,7 @@
         <v>33</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1053,7 +1053,7 @@
         <v>32</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1064,11 +1064,11 @@
     <hyperlink ref="A3" r:id="rId1" xr:uid="{F02B61D7-72B9-4D2E-B915-44297625D2AF}"/>
     <hyperlink ref="A4" r:id="rId2" xr:uid="{6ED0707E-1A3D-41DE-9D1F-0C185E1F4903}"/>
     <hyperlink ref="A5" r:id="rId3" xr:uid="{A88A08DE-BC8D-44F4-B4A3-F3F45BEED893}"/>
-    <hyperlink ref="B2" r:id="rId4" xr:uid="{88D13356-CD0F-4958-BE46-AB501B49D616}"/>
-    <hyperlink ref="B3" r:id="rId5" xr:uid="{D45C86F9-3A86-447F-9A88-FC4ADCDA713E}"/>
-    <hyperlink ref="B4" r:id="rId6" xr:uid="{231CB918-F83F-4617-B02E-DB0243B4B153}"/>
-    <hyperlink ref="B5" r:id="rId7" xr:uid="{DF0DBB8C-862D-49E8-9462-6A3EC6EBF8BD}"/>
-    <hyperlink ref="B6" r:id="rId8" xr:uid="{7871CE11-05D2-4010-9B4E-5D590A4E3BA6}"/>
+    <hyperlink ref="B6" r:id="rId4" xr:uid="{7871CE11-05D2-4010-9B4E-5D590A4E3BA6}"/>
+    <hyperlink ref="B5" r:id="rId5" xr:uid="{F5146C6D-3127-4C5E-9E17-6BA716A788C8}"/>
+    <hyperlink ref="B4" r:id="rId6" xr:uid="{315BCF2A-F5E6-4DAF-AB7F-E6E7B323A234}"/>
+    <hyperlink ref="B3" r:id="rId7" xr:uid="{46D09166-B6A7-4F8A-82CF-3FADE30BFF70}"/>
+    <hyperlink ref="B2" r:id="rId8" xr:uid="{7E48E583-A31E-4D3D-A449-5AEB5AB8F36A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId9"/>
@@ -1097,7 +1097,7 @@
         <v>31</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1108,7 +1108,7 @@
         <v>31</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1119,7 +1119,7 @@
         <v>45</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1130,7 +1130,7 @@
         <v>45</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1141,7 +1141,7 @@
         <v>45</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1153,10 +1153,10 @@
     <hyperlink ref="A5" r:id="rId2" xr:uid="{49CDF971-88A0-478A-9ABD-0C13B137739B}"/>
     <hyperlink ref="A6" r:id="rId3" xr:uid="{DD33285A-BEC3-43E6-9CF7-C07B547F86A0}"/>
     <hyperlink ref="B2" r:id="rId4" xr:uid="{E884574A-2EFB-4087-B99B-32D65C06622B}"/>
-    <hyperlink ref="B3" r:id="rId5" xr:uid="{CE317B36-AFD3-47B8-9712-C8FD0B60611E}"/>
-    <hyperlink ref="B4" r:id="rId6" xr:uid="{3F400C4D-CB90-42C3-8827-DD9CFB7EEF17}"/>
-    <hyperlink ref="B5" r:id="rId7" xr:uid="{EC448C53-A56A-483F-BFDC-393AA3AD6739}"/>
-    <hyperlink ref="B6" r:id="rId8" xr:uid="{0C92C735-4C59-4494-8A27-87675DF9C5C1}"/>
+    <hyperlink ref="B4" r:id="rId5" xr:uid="{3F400C4D-CB90-42C3-8827-DD9CFB7EEF17}"/>
+    <hyperlink ref="B3" r:id="rId6" xr:uid="{2EE1A7D7-D54B-40BE-82E0-7ABA4E2B4022}"/>
+    <hyperlink ref="B5" r:id="rId7" xr:uid="{51A20BA4-5967-48B8-A04F-F54B5A797908}"/>
+    <hyperlink ref="B6" r:id="rId8" xr:uid="{A37ADBBB-1AC9-40D9-9C81-C3173252FC8A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId9"/>

--- a/TestData/LV_T2279_TMTI0036293_ApproveEventExpenseFormAsSecondLevelApproverSet1.xlsx
+++ b/TestData/LV_T2279_TMTI0036293_ApproveEventExpenseFormAsSecondLevelApproverSet1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D89474-4C8A-4D5B-9E1A-17D7858EB171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1144EA31-FEA5-42FF-AD5F-5BBB2208D995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -534,17 +534,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>52</v>
       </c>
@@ -552,7 +552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>34</v>
       </c>
@@ -560,7 +560,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>34</v>
       </c>
@@ -568,7 +568,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>34</v>
       </c>
@@ -576,7 +576,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>52</v>
       </c>
@@ -592,14 +592,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{780E0E82-BFFE-42FB-A31B-AC0D9C5DE596}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>49</v>
       </c>
@@ -612,14 +612,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D588DDF-4567-4D40-8446-D6AC9693F696}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>51</v>
       </c>
@@ -632,25 +632,25 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -701,7 +701,7 @@
       </c>
       <c r="Q1" s="1"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -757,7 +757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -813,7 +813,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -869,7 +869,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -925,7 +925,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -990,13 +990,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
@@ -1004,7 +1004,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>32</v>
       </c>
@@ -1015,7 +1015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>33</v>
       </c>
@@ -1026,7 +1026,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>33</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>33</v>
       </c>
@@ -1048,7 +1048,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -1078,13 +1078,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
@@ -1092,7 +1092,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>31</v>
       </c>
@@ -1103,7 +1103,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -1114,7 +1114,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>45</v>
       </c>
@@ -1125,7 +1125,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>45</v>
       </c>
@@ -1136,7 +1136,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>45</v>
       </c>

--- a/TestData/LV_T2279_TMTI0036293_ApproveEventExpenseFormAsSecondLevelApproverSet1.xlsx
+++ b/TestData/LV_T2279_TMTI0036293_ApproveEventExpenseFormAsSecondLevelApproverSet1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1144EA31-FEA5-42FF-AD5F-5BBB2208D995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C85A2D3-13FF-4D87-B17B-2AA6A675FB72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -194,7 +194,7 @@
     <t>FVATestOpportunity Admin</t>
   </si>
   <si>
-    <t>Bingo@123456</t>
+    <t>Bingo@12345</t>
   </si>
 </sst>
 </file>
@@ -534,17 +534,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>52</v>
       </c>
@@ -552,7 +552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>34</v>
       </c>
@@ -560,7 +560,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>34</v>
       </c>
@@ -568,7 +568,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>34</v>
       </c>
@@ -576,7 +576,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>52</v>
       </c>
@@ -592,14 +592,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{780E0E82-BFFE-42FB-A31B-AC0D9C5DE596}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>49</v>
       </c>
@@ -612,14 +612,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D588DDF-4567-4D40-8446-D6AC9693F696}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>51</v>
       </c>
@@ -632,25 +632,25 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -701,7 +701,7 @@
       </c>
       <c r="Q1" s="1"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -757,7 +757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -813,7 +813,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -869,7 +869,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -925,7 +925,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -990,13 +990,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
@@ -1004,7 +1004,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>32</v>
       </c>
@@ -1015,7 +1015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>33</v>
       </c>
@@ -1026,7 +1026,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>33</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>33</v>
       </c>
@@ -1048,7 +1048,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -1064,11 +1064,11 @@
     <hyperlink ref="A3" r:id="rId1" xr:uid="{F02B61D7-72B9-4D2E-B915-44297625D2AF}"/>
     <hyperlink ref="A4" r:id="rId2" xr:uid="{6ED0707E-1A3D-41DE-9D1F-0C185E1F4903}"/>
     <hyperlink ref="A5" r:id="rId3" xr:uid="{A88A08DE-BC8D-44F4-B4A3-F3F45BEED893}"/>
-    <hyperlink ref="B6" r:id="rId4" xr:uid="{7871CE11-05D2-4010-9B4E-5D590A4E3BA6}"/>
-    <hyperlink ref="B5" r:id="rId5" xr:uid="{F5146C6D-3127-4C5E-9E17-6BA716A788C8}"/>
-    <hyperlink ref="B4" r:id="rId6" xr:uid="{315BCF2A-F5E6-4DAF-AB7F-E6E7B323A234}"/>
-    <hyperlink ref="B3" r:id="rId7" xr:uid="{46D09166-B6A7-4F8A-82CF-3FADE30BFF70}"/>
-    <hyperlink ref="B2" r:id="rId8" xr:uid="{7E48E583-A31E-4D3D-A449-5AEB5AB8F36A}"/>
+    <hyperlink ref="B2" r:id="rId4" xr:uid="{7E48E583-A31E-4D3D-A449-5AEB5AB8F36A}"/>
+    <hyperlink ref="B3" r:id="rId5" xr:uid="{BFBA4B09-5F16-49CA-8382-DEDD86265CE9}"/>
+    <hyperlink ref="B4" r:id="rId6" xr:uid="{7A1519DD-7B79-48DE-81D2-7D041A1AF37E}"/>
+    <hyperlink ref="B5" r:id="rId7" xr:uid="{1E8B7BC1-EAF1-48C4-AF7B-EA5467C230C3}"/>
+    <hyperlink ref="B6" r:id="rId8" xr:uid="{D3FB8478-6724-494B-B54D-0D5303E6D17C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId9"/>
@@ -1078,13 +1078,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
@@ -1092,7 +1092,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>31</v>
       </c>
@@ -1103,7 +1103,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -1114,7 +1114,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>45</v>
       </c>
@@ -1125,7 +1125,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>45</v>
       </c>
@@ -1136,7 +1136,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>45</v>
       </c>
@@ -1153,10 +1153,10 @@
     <hyperlink ref="A5" r:id="rId2" xr:uid="{49CDF971-88A0-478A-9ABD-0C13B137739B}"/>
     <hyperlink ref="A6" r:id="rId3" xr:uid="{DD33285A-BEC3-43E6-9CF7-C07B547F86A0}"/>
     <hyperlink ref="B2" r:id="rId4" xr:uid="{E884574A-2EFB-4087-B99B-32D65C06622B}"/>
-    <hyperlink ref="B4" r:id="rId5" xr:uid="{3F400C4D-CB90-42C3-8827-DD9CFB7EEF17}"/>
-    <hyperlink ref="B3" r:id="rId6" xr:uid="{2EE1A7D7-D54B-40BE-82E0-7ABA4E2B4022}"/>
-    <hyperlink ref="B5" r:id="rId7" xr:uid="{51A20BA4-5967-48B8-A04F-F54B5A797908}"/>
-    <hyperlink ref="B6" r:id="rId8" xr:uid="{A37ADBBB-1AC9-40D9-9C81-C3173252FC8A}"/>
+    <hyperlink ref="B3" r:id="rId5" xr:uid="{EAC6C758-3FC6-4850-B067-CDA69A9D42D1}"/>
+    <hyperlink ref="B4" r:id="rId6" xr:uid="{53E34E7E-E337-4F6A-B604-0191D4279933}"/>
+    <hyperlink ref="B5" r:id="rId7" xr:uid="{82074175-0EBB-4988-8186-1E85DAF85604}"/>
+    <hyperlink ref="B6" r:id="rId8" xr:uid="{92389FF4-ECF0-423A-A5BE-244988A95264}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId9"/>
